--- a/New_Updates/COMB model - updated.xlsx
+++ b/New_Updates/COMB model - updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AMBEON\script\backend\New_Updates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF9190A-EF79-4258-87D4-930DBC91AAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FB42B4-92C1-4731-9977-CA10BCB84468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{93A02624-0DC0-4080-9159-B3C756B21157}"/>
   </bookViews>
@@ -20,6 +20,7 @@
     <sheet name="Ratios" sheetId="11" r:id="rId5"/>
     <sheet name="Quarterly" sheetId="9" r:id="rId6"/>
     <sheet name="Sheet1" sheetId="10" r:id="rId7"/>
+    <sheet name="Sheet2" sheetId="12" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">Drivers!$A$107:$H$520</definedName>
@@ -10565,7 +10566,8 @@
         <v>-4218</v>
       </c>
       <c r="E125" s="22">
-        <v>-4988</v>
+        <f>-L119</f>
+        <v>0</v>
       </c>
       <c r="F125" s="121"/>
       <c r="G125" s="22">
@@ -35362,6 +35364,7 @@
   <dimension ref="A1:E132"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="26" customWidth="1"/>
     <col min="5" max="5" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -37071,4 +37074,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8161DB-789F-49B4-BA4A-31A5BB501C32}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>